--- a/output/TEST_CLASSIC_ecog_zero.xlsx
+++ b/output/TEST_CLASSIC_ecog_zero.xlsx
@@ -184,49 +184,49 @@
     <t xml:space="preserve">Data Complete</t>
   </si>
   <si>
-    <t xml:space="preserve">&amp;id=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&amp;id=49</t>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://redcap.fake.edu/redcap_v16.1.4/DataEntry/record_home.php?pid=12341&amp;id=49</t>
   </si>
   <si>
     <t xml:space="preserve">record_id</t>
@@ -364,7 +364,7 @@
     <t xml:space="preserve">ctcae5:C57293</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-02-15</t>
+    <t xml:space="preserve">2025-09-18</t>
   </si>
   <si>
     <t xml:space="preserve">2025-11-19 19:55:00</t>
@@ -436,10 +436,10 @@
     <t xml:space="preserve">IV</t>
   </si>
   <si>
-    <t xml:space="preserve">2019-05-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-25</t>
+    <t xml:space="preserve">2018-12-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-07-28</t>
   </si>
   <si>
     <t xml:space="preserve">Complete</t>
@@ -448,13 +448,13 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-02-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-12</t>
+    <t xml:space="preserve">2024-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-11-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-14</t>
   </si>
   <si>
     <t xml:space="preserve">2024-11-15 17:58:00</t>
@@ -502,22 +502,22 @@
     <t xml:space="preserve">False</t>
   </si>
   <si>
-    <t xml:space="preserve">2020-12-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-21</t>
+    <t xml:space="preserve">2020-08-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-05-24</t>
   </si>
   <si>
     <t xml:space="preserve">15</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-02</t>
+    <t xml:space="preserve">2023-12-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-05</t>
   </si>
   <si>
     <t xml:space="preserve">2024-06-17 05:55:00</t>
@@ -556,19 +556,19 @@
     <t xml:space="preserve">II</t>
   </si>
   <si>
-    <t xml:space="preserve">2018-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2021-01-19</t>
+    <t xml:space="preserve">2018-02-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-08-22</t>
   </si>
   <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-07-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-24</t>
+    <t xml:space="preserve">2024-02-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-27</t>
   </si>
   <si>
     <t xml:space="preserve">2024-05-22 14:45:00</t>
@@ -607,19 +607,19 @@
     <t xml:space="preserve">has,comma</t>
   </si>
   <si>
-    <t xml:space="preserve">2021-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-12-08</t>
+    <t xml:space="preserve">2021-01-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-07-11</t>
   </si>
   <si>
     <t xml:space="preserve">18</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-10-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-06</t>
+    <t xml:space="preserve">2024-05-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-07</t>
   </si>
   <si>
     <t xml:space="preserve">2024-05-14 18:01:00</t>
@@ -658,22 +658,22 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">2021-03-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-02</t>
+    <t xml:space="preserve">2020-10-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-03</t>
   </si>
   <si>
     <t xml:space="preserve">29</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-11-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-17</t>
+    <t xml:space="preserve">2024-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-20</t>
   </si>
   <si>
     <t xml:space="preserve">2024-11-10 01:04:00</t>
@@ -709,366 +709,366 @@
     <t xml:space="preserve">III</t>
   </si>
   <si>
-    <t xml:space="preserve">2021-04-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-20</t>
+    <t xml:space="preserve">2020-11-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-21</t>
   </si>
   <si>
     <t xml:space="preserve">30</t>
   </si>
   <si>
-    <t xml:space="preserve">2024-07-09</t>
+    <t xml:space="preserve">2024-02-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-20 19:01:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-12 21:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-26 18:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-27 14:40:35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-17 03:39:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">h</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:22:33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:27:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has, ,comma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-04-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-02-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-02 22:15:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-06 02:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-23 21:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-12 02:14:49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01-22 00:11:07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">04:48:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:28:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-10-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-11-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-21 01:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-03 12:44:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-19 02:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-31 17:02:25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-24 00:36:43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13:51:48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20:03:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-18 22:10:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-30 12:53:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-23 12:24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-05 18:58:44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-10 07:40:05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10:08:13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16:42:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-03-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-12-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-28 06:30:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-29 16:19:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-18 06:11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-08 04:21:34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-07 14:42:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07:42:56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:54:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-04-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08-03 12:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-17 18:46:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-11 22:09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-16 14:28:21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-21 02:38:06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11:43:54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12:11:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">180</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-04-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2028-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-01 11:20:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-03 03:37:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10-12 10:36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-22 01:31:39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09-08 06:55:22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">r</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14:59:15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22:18:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-01-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-04-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47</t>
   </si>
   <si>
     <t xml:space="preserve">2024-06-22</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-03-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-20 19:01:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-12 21:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-26 18:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-27 14:40:35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-17 03:39:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">99.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:22:33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:27:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has, ,comma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-02 22:15:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-06 02:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-23 21:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-12 02:14:49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-01-22 00:11:07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">04:48:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:28:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-01-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-03-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-21 01:42:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-03 12:44:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-19 02:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-31 17:02:25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-24 00:36:43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">o</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13:51:48</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20:03:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-02-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-02-21</t>
+    <t xml:space="preserve">2024-04-06</t>
   </si>
   <si>
     <t xml:space="preserve">2024-08-18</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-02-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-18 22:10:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-30 12:53:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-23 12:24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-05 18:58:44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-10 07:40:05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10:08:13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:42:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2018-08-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019-02-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-05-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-28 06:30:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-29 16:19:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-18 06:11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-08 04:21:34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-02-07 14:42:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">07:42:56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:54:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-08-03 12:26:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-17 18:46:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-04-11 22:09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-07-16 14:28:21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-21 02:38:06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11:43:54</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12:11:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">180</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2023-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2029-01-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-01 11:20:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-03 03:37:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-12 10:36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-06-22 01:31:39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-08 06:55:22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14:59:15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22:18:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-06-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-15</t>
-  </si>
-  <si>
     <t xml:space="preserve">2024-03-16 00:20:00</t>
   </si>
   <si>
@@ -1102,22 +1102,22 @@
     <t xml:space="preserve">153</t>
   </si>
   <si>
-    <t xml:space="preserve">2021-11-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-03</t>
+    <t xml:space="preserve">2021-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-05-06</t>
   </si>
   <si>
     <t xml:space="preserve">49</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-01-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-10-21</t>
+    <t xml:space="preserve">2024-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05-24</t>
   </si>
   <si>
     <t xml:space="preserve">2024-08-24 18:46:00</t>
@@ -1153,10 +1153,10 @@
     <t xml:space="preserve">81</t>
   </si>
   <si>
-    <t xml:space="preserve">2023-01-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2027-05-10</t>
+    <t xml:space="preserve">2022-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-11</t>
   </si>
   <si>
     <t xml:space="preserve">form_name</t>
@@ -1969,7 +1969,7 @@
     <t xml:space="preserve">last_save_time</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-06 08:05:01.888065</t>
+    <t xml:space="preserve">2026-05-10 15:18:59.588024</t>
   </si>
   <si>
     <t xml:space="preserve">final_form_tab_names</t>
